--- a/public/import_template/v0.2node/node_module_media.xlsx
+++ b/public/import_template/v0.2node/node_module_media.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ddit\code\umi_max.250519_master\public\import_template\v0.2node\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ddit\code\umi_max.260226_github\public\import_template\v0.2node\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98706A8-F479-4912-8F29-0D70463C3E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DEF72A-78B8-4433-AAA2-D78B06A170FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="762" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="762" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表" sheetId="8" r:id="rId1"/>
@@ -654,7 +654,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -751,12 +751,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -802,7 +796,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -892,19 +886,13 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1419,10 +1407,10 @@
       <c r="G10" s="23"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="33" t="s">
         <v>143</v>
       </c>
       <c r="C11" s="24" t="s">
@@ -1434,10 +1422,10 @@
       <c r="G11" s="23"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="33" t="s">
         <v>145</v>
       </c>
       <c r="C12" s="24" t="s">
@@ -1822,65 +1810,65 @@
       <c r="AJ2" s="34"/>
     </row>
     <row r="3" spans="1:36" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="1">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="2">
         <v>1</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
       </c>
-      <c r="H3" s="1"/>
+      <c r="H3" s="2"/>
       <c r="I3" s="2">
         <v>120</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="1" t="s">
+      <c r="J3" s="2"/>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-      <c r="AG3" s="1"/>
-      <c r="AH3" s="1"/>
-      <c r="AI3" s="1" t="s">
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="2"/>
+      <c r="AE3" s="2"/>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2"/>
+      <c r="AH3" s="2"/>
+      <c r="AI3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AJ3" s="1"/>
+      <c r="AJ3" s="2"/>
     </row>
     <row r="4" spans="1:36" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1900,7 +1888,7 @@
         <v>280</v>
       </c>
       <c r="J4" s="2"/>
-      <c r="K4" s="1"/>
+      <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2" t="s">
@@ -1913,13 +1901,13 @@
       <c r="S4" s="5"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
-      <c r="V4" s="1"/>
+      <c r="V4" s="2"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
       <c r="Y4" s="2">
         <v>1</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="Z4" s="2" t="s">
         <v>39</v>
       </c>
       <c r="AA4" s="2"/>
@@ -1940,7 +1928,7 @@
       </c>
     </row>
     <row r="5" spans="1:36" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1975,13 +1963,13 @@
       <c r="S5" s="5"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
-      <c r="V5" s="1"/>
+      <c r="V5" s="2"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
       <c r="Y5" s="2">
         <v>1</v>
       </c>
-      <c r="Z5" s="1" t="s">
+      <c r="Z5" s="2" t="s">
         <v>39</v>
       </c>
       <c r="AA5" s="2"/>
@@ -2002,7 +1990,7 @@
       </c>
     </row>
     <row r="6" spans="1:36" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -2023,7 +2011,7 @@
         <v>38</v>
       </c>
       <c r="K6" s="2"/>
-      <c r="L6" s="1">
+      <c r="L6" s="2">
         <v>1</v>
       </c>
       <c r="M6" s="2" t="s">
@@ -2041,13 +2029,13 @@
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
-      <c r="V6" s="1"/>
+      <c r="V6" s="2"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="2">
         <v>1</v>
       </c>
-      <c r="Z6" s="1" t="s">
+      <c r="Z6" s="2" t="s">
         <v>39</v>
       </c>
       <c r="AA6" s="2"/>
@@ -2066,7 +2054,7 @@
       </c>
     </row>
     <row r="7" spans="1:36" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -2086,10 +2074,10 @@
         <v>180</v>
       </c>
       <c r="J7" s="2"/>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1">
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2">
         <v>1</v>
       </c>
       <c r="M7" s="2"/>
@@ -2101,13 +2089,13 @@
       <c r="S7" s="5"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
-      <c r="V7" s="1"/>
+      <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
       <c r="Y7" s="2">
         <v>1</v>
       </c>
-      <c r="Z7" s="1" t="s">
+      <c r="Z7" s="2" t="s">
         <v>39</v>
       </c>
       <c r="AA7" s="2"/>
@@ -2128,7 +2116,7 @@
       </c>
     </row>
     <row r="8" spans="1:36" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2148,7 +2136,7 @@
         <v>100</v>
       </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="1">
+      <c r="K8" s="2">
         <v>1</v>
       </c>
       <c r="L8" s="2"/>
@@ -2161,13 +2149,13 @@
       <c r="S8" s="5"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
-      <c r="V8" s="1"/>
+      <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
       <c r="Y8" s="2">
         <v>1</v>
       </c>
-      <c r="Z8" s="1" t="s">
+      <c r="Z8" s="2" t="s">
         <v>39</v>
       </c>
       <c r="AA8" s="2"/>
@@ -2188,7 +2176,7 @@
       </c>
     </row>
     <row r="9" spans="1:36" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -2217,7 +2205,7 @@
       <c r="S9" s="5"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
-      <c r="V9" s="1"/>
+      <c r="V9" s="2"/>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
       <c r="Y9" s="2">
@@ -2242,7 +2230,7 @@
       </c>
     </row>
     <row r="10" spans="1:36" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -2263,7 +2251,7 @@
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="1">
+      <c r="L10" s="2">
         <v>1</v>
       </c>
       <c r="M10" s="2"/>
@@ -2279,7 +2267,7 @@
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
-      <c r="V10" s="1"/>
+      <c r="V10" s="2"/>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
       <c r="Y10" s="2">
@@ -2304,13 +2292,13 @@
       </c>
     </row>
     <row r="11" spans="1:36" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="33" t="s">
         <v>153</v>
       </c>
       <c r="D11" s="6"/>
@@ -2325,34 +2313,34 @@
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="1">
-        <v>1</v>
-      </c>
-      <c r="M11" s="37" t="s">
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+      <c r="M11" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="N11" s="36" t="s">
+      <c r="N11" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
-      <c r="V11" s="1"/>
+      <c r="V11" s="2"/>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
-      <c r="Y11" s="36">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="36" t="s">
+      <c r="Y11" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="2" t="s">
         <v>39</v>
       </c>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2"/>
-      <c r="AC11" s="36" t="s">
+      <c r="AC11" s="2" t="s">
         <v>149</v>
       </c>
       <c r="AD11" s="2"/>
@@ -2366,13 +2354,13 @@
       </c>
     </row>
     <row r="12" spans="1:36" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="33" t="s">
         <v>145</v>
       </c>
       <c r="D12" s="6"/>
@@ -2389,38 +2377,38 @@
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="1">
-        <v>1</v>
-      </c>
-      <c r="M12" s="37" t="s">
+      <c r="L12" s="2">
+        <v>1</v>
+      </c>
+      <c r="M12" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="N12" s="36" t="s">
+      <c r="N12" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36" t="s">
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="S12" s="36" t="s">
+      <c r="S12" s="2" t="s">
         <v>148</v>
       </c>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
-      <c r="V12" s="1"/>
+      <c r="V12" s="2"/>
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
-      <c r="Y12" s="36">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="36" t="s">
+      <c r="Y12" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="2" t="s">
         <v>39</v>
       </c>
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
-      <c r="AC12" s="36" t="s">
+      <c r="AC12" s="2" t="s">
         <v>149</v>
       </c>
       <c r="AD12" s="2"/>
@@ -2625,7 +2613,7 @@
       <c r="G1" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="21" t="s">
         <v>136</v>
       </c>
       <c r="I1" s="21" t="s">
@@ -2638,5 +2626,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>